--- a/astro-site/public/dl/restaurant-checklist-templates/BONUS-02-restaurant-holiday-calendar.xlsx
+++ b/astro-site/public/dl/restaurant-checklist-templates/BONUS-02-restaurant-holiday-calendar.xlsx
@@ -662,7 +662,7 @@
     <row r="12" ht="31" customHeight="1">
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the FRAME of the day.</t>
+          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the BACKBONE of the day.</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>Super Bowl Sunday (early Feb)</t>
+          <t>Super Bowl Sunday (2nd Sunday in Feb)</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>Labor Day + back to school</t>
+          <t>Labor Day (1st Monday) + back to school</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
